--- a/model_templates/ark.OlinkFileAnnotationTemplate.xlsx
+++ b/model_templates/ark.OlinkFileAnnotationTemplate.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
-    <sheet state="hidden" name="Sheet2" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet state="hidden" name="Sheet2" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -5042,7 +5042,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
   <si>
     <t>Component</t>
   </si>
@@ -5084,6 +5084,9 @@
   </si>
   <si>
     <t>figure</t>
+  </si>
+  <si>
+    <t>unknown</t>
   </si>
   <si>
     <t>bim</t>
@@ -5138,6 +5141,9 @@
   </si>
   <si>
     <t>pdf</t>
+  </si>
+  <si>
+    <t>py</t>
   </si>
   <si>
     <t>rds</t>
@@ -5269,6 +5275,10 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -32494,13 +32504,13 @@
   </sheetData>
   <dataValidations>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="E2:E1000">
-      <formula1>Sheet2!$E$2:$E$3</formula1>
+      <formula1>Sheet2!$E$2:$E$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="B2:B1000">
+      <formula1>Sheet2!$B$2:$B$33</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="C2:C1000">
       <formula1>Sheet2!$C$2:$C$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Choose one from dropdown" sqref="B2:B1000">
-      <formula1>Sheet2!$B$2:$B$32</formula1>
     </dataValidation>
   </dataValidations>
   <drawing r:id="rId2"/>
@@ -32561,148 +32571,156 @@
       <c r="C4" s="6" t="s">
         <v>13</v>
       </c>
+      <c r="E4" s="6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="6" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
